--- a/翻译/翻译_多语言翻译表_韩文.xlsx
+++ b/翻译/翻译_多语言翻译表_韩文.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>::ID::</t>
   </si>
@@ -71,40 +71,46 @@
     <t>::JP::</t>
   </si>
   <si>
-    <t>Task_optimization15</t>
-  </si>
-  <si>
-    <t>({0}秒后自动关闭)</t>
-  </si>
-  <si>
-    <t>({0}초 후 자동 종료)</t>
-  </si>
-  <si>
-    <t>NEW_1v1_Des5</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>상점1</t>
-  </si>
-  <si>
-    <t>D8_SSCM_Text18</t>
-  </si>
-  <si>
-    <t>挑战</t>
-  </si>
-  <si>
-    <t>도전</t>
-  </si>
-  <si>
-    <t>D8_ShengWu_Text40</t>
-  </si>
-  <si>
-    <t>属性</t>
-  </si>
-  <si>
-    <t>속성</t>
+    <t>暂无公会分组</t>
+  </si>
+  <si>
+    <t>暂无参赛公会</t>
+  </si>
+  <si>
+    <t>暂无参赛玩家</t>
+  </si>
+  <si>
+    <t>当前不是报名阶段哦</t>
+  </si>
+  <si>
+    <t>不能重复报名哦</t>
+  </si>
+  <si>
+    <t>您没有权限报名哦</t>
+  </si>
+  <si>
+    <t>公会人数不足</t>
+  </si>
+  <si>
+    <t>当前不是挑战阶段哦</t>
+  </si>
+  <si>
+    <t>您没有参赛资格</t>
+  </si>
+  <si>
+    <t>挑战次数不足</t>
+  </si>
+  <si>
+    <t>对方生命数不足</t>
+  </si>
+  <si>
+    <t>对方正在被挑战</t>
+  </si>
+  <si>
+    <t>对方服务器异常</t>
+  </si>
+  <si>
+    <t>进入地图错误</t>
   </si>
 </sst>
 </file>
@@ -117,13 +123,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -590,141 +602,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -777,7 +795,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -971,25 +996,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1008,7 +1033,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1250,8 +1275,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="27.125" style="1" customWidth="1"/>
   </cols>
@@ -1301,55 +1326,123 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" t="s">
+      <c r="A2" s="2">
+        <v>26701</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
+      <c r="A3" s="2">
+        <v>26702</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
+      <c r="A4" s="2">
+        <v>26703</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" t="s">
+      <c r="A5" s="2">
+        <v>26704</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="2">
+        <v>26705</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="2">
+        <v>26706</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2">
+        <v>26707</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="2">
+        <v>26708</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="2">
+        <v>26709</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="2">
+        <v>26710</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="2">
+        <v>26711</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L5" t="s">
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="2">
+        <v>26712</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="2">
+        <v>26713</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="2">
+        <v>26714</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" priority="2"/>
+    <cfRule type="duplicateValues" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A5">
-    <cfRule type="duplicateValues" priority="1"/>
+  <conditionalFormatting sqref="A2:A15">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
